--- a/data/fav_hisse_senetleri.xlsx
+++ b/data/fav_hisse_senetleri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enesa\Desktop\financial_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B1BFA8-87EF-4CD7-A19D-868D40C420FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A1C51F-95EF-42D0-A96F-F45E679D3098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>AHSGY</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>Sirket</t>
+  </si>
+  <si>
+    <t>GLRMK</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -514,6 +517,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:A618" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
